--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -13225,10 +13225,10 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>75</v>
@@ -13423,10 +13423,10 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>75</v>
@@ -13522,10 +13522,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>75</v>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
